--- a/hisobotlar/Shtat xodimlar royxati.xlsx
+++ b/hisobotlar/Shtat xodimlar royxati.xlsx
@@ -461,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -472,9 +472,11 @@
     <col width="30" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="34" customWidth="1" min="9" max="9"/>
-    <col width="28" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="11" max="11"/>
+    <col width="28" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -527,15 +529,25 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
+          <t>INN (STIR)</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Plastik karta raqami</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
           <t>Tamomlagan OTM / Ta'lim muassasasi</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>Diplom bo'yicha mutaxassisligi</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>Ishga kirgan buyruq sanasi</t>
         </is>
@@ -580,17 +592,23 @@
           <t>31211832710036</t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr"/>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>9860080311468542</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
         <is>
           <t>Mirzo Ulug'bek nomidagi O'zbekiston Milliy universiteti</t>
         </is>
       </c>
-      <c r="J3" s="4" t="inlineStr">
+      <c r="L3" s="4" t="inlineStr">
         <is>
           <t>Ijtimoiy tizimlar va jarayonlarning axborot psixalogik xavfsizligi</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
+      <c r="M3" s="3" t="inlineStr">
         <is>
           <t>28.08.2026</t>
         </is>
@@ -635,9 +653,15 @@
           <t>31008932640046</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr"/>
-      <c r="J4" s="4" t="inlineStr"/>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr"/>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>9860080311717658</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr"/>
+      <c r="L4" s="4" t="inlineStr"/>
+      <c r="M4" s="3" t="inlineStr">
         <is>
           <t>28.08.2026</t>
         </is>
@@ -682,9 +706,15 @@
           <t>51207055730023</t>
         </is>
       </c>
-      <c r="I5" s="4" t="inlineStr"/>
-      <c r="J5" s="4" t="inlineStr"/>
-      <c r="K5" s="3" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr"/>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>9860080311682803</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr"/>
+      <c r="L5" s="4" t="inlineStr"/>
+      <c r="M5" s="3" t="inlineStr">
         <is>
           <t>28.08.2026</t>
         </is>
@@ -729,9 +759,15 @@
           <t>32805622730035</t>
         </is>
       </c>
-      <c r="I6" s="4" t="inlineStr"/>
-      <c r="J6" s="4" t="inlineStr"/>
-      <c r="K6" s="3" t="inlineStr">
+      <c r="I6" s="3" t="inlineStr"/>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>9860080311417465</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr"/>
+      <c r="L6" s="4" t="inlineStr"/>
+      <c r="M6" s="3" t="inlineStr">
         <is>
           <t>28.08.2026</t>
         </is>
@@ -776,9 +812,15 @@
           <t>43004787890011</t>
         </is>
       </c>
-      <c r="I7" s="4" t="inlineStr"/>
-      <c r="J7" s="4" t="inlineStr"/>
-      <c r="K7" s="3" t="inlineStr">
+      <c r="I7" s="3" t="inlineStr"/>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>9860080311516175</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="inlineStr"/>
+      <c r="L7" s="4" t="inlineStr"/>
+      <c r="M7" s="3" t="inlineStr">
         <is>
           <t>28.08.2026</t>
         </is>
@@ -823,9 +865,15 @@
           <t>41111892560099</t>
         </is>
       </c>
-      <c r="I8" s="4" t="inlineStr"/>
-      <c r="J8" s="4" t="inlineStr"/>
-      <c r="K8" s="3" t="inlineStr">
+      <c r="I8" s="3" t="inlineStr"/>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>9860080311452975</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr"/>
+      <c r="L8" s="4" t="inlineStr"/>
+      <c r="M8" s="3" t="inlineStr">
         <is>
           <t>28.08.2026</t>
         </is>
@@ -870,9 +918,11 @@
           <t>31501815560016</t>
         </is>
       </c>
-      <c r="I9" s="4" t="inlineStr"/>
-      <c r="J9" s="4" t="inlineStr"/>
-      <c r="K9" s="3" t="inlineStr">
+      <c r="I9" s="3" t="inlineStr"/>
+      <c r="J9" s="3" t="inlineStr"/>
+      <c r="K9" s="4" t="inlineStr"/>
+      <c r="L9" s="4" t="inlineStr"/>
+      <c r="M9" s="3" t="inlineStr">
         <is>
           <t>28.08.2026</t>
         </is>
@@ -917,9 +967,15 @@
           <t>62603005590051</t>
         </is>
       </c>
-      <c r="I10" s="4" t="inlineStr"/>
-      <c r="J10" s="4" t="inlineStr"/>
-      <c r="K10" s="3" t="inlineStr">
+      <c r="I10" s="3" t="inlineStr"/>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>9860080311950358</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr"/>
+      <c r="L10" s="4" t="inlineStr"/>
+      <c r="M10" s="3" t="inlineStr">
         <is>
           <t>28.08.2026</t>
         </is>
@@ -927,7 +983,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A1:M1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
